--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1268,8 +1268,824 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>b100518e138a4eb9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.537865</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>-0.0216063656387665</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:22.804516Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>7da3455a651d49bd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.518772</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.09860393277310925</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:23.359845Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>52801cc437094db0</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.626584</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>-0.013703769784172648</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:23.904156Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>8438ac268e814b31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:24.994619Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>b67a1d3197114a19</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67658</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.692093</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>-0.007606699699699737</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:26.008727Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>8b82932193b64616</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.051011431924882666</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:26.573553Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>feb3f1f090954168</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:27.625205Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6fcc3c4b3c9d4ffc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.563407</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.0365930000000001</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:29.848917Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ7"/>
+  <autoFilter ref="A1:AJ15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2084,8 +2084,1538 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>db0288d455db4fe1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.537865</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>-0.0216063656387665</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:42.885962Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9d0d33703c734f3c</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.518772</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.09860393277310925</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:43.343807Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>a1378c2244f6468a</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.626584</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.013703769784172648</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:43.839495Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>5f5b650e1b534703</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:45.187026Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3295b1de187f44ae</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>67658</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.692093</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>-0.007606699699699737</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:46.115122Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>64d8a0204ab449fb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.051011431924882666</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:46.601400Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>a94cc93c626a408d</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:47.634612Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>152d1d6289344945</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>eeff6515a3cbe0e3aedb7fd70fb4721914ccca5c50ad69a370208fe6051de3a7</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.563407</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>-0.07688076978417269</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:49.578306Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>0077d8752cf8412c</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.537865</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.0216063656387665</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:41.949275Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>c484dbcf978a44e5</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.518772</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.09860393277310925</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:42.402563Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>4c6f457d2cfa45e4</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.626584</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.013703769784172648</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:42.939409Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>0c3b11f700f24239</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.08467381789137385</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:43.967259Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>79e9778e7c3a4a43</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.051011431924882666</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:45.603247Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>5c4310421db0489e</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:46.542257Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>bf3b0e9a944345b6</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.563407</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>-0.07688076978417269</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:48.544086Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ15"/>
+  <autoFilter ref="A1:AJ30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3614,8 +3614,620 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>20b0edbe54604ac2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.537865</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>-0.0216063656387665</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:49.680825Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>41bf3866931946b3</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.518772</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.09860393277310925</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:50.165415Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2c67c7be093c4d98</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.626584</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>-0.013703769784172648</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:50.730936Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>f2b74b8728a54584</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.765185</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.07478252321981427</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:51.807690Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>de993eb0840a4035</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.11065893442622954</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:53.324618Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>a5a75fc6f2934739</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:54.386243Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ30"/>
+  <autoFilter ref="A1:AJ36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4226,8 +4226,620 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>57ccc068d8404e59</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.518775</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.09860693277310922</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:18.656978Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>5e78797afa29455d</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.626621</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>-0.013666769784172694</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:19.194193Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>73e094743e8b4de3</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:20.414393Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>477a600499b34205</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.11065893442622954</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:21.952693Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>f76898ecba834883</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:22.943314Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ca2579187c5f4763</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>68095</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.519652</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.14928162962962965</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:23.897138Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ36"/>
+  <autoFilter ref="A1:AJ42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4838,8 +4838,620 @@
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>fa25b6b5cd8c476a</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.518775</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.09860693277310922</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:07.245341Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>0f89a28245da44f9</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>67386</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.626621</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.013666769784172694</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:07.777596Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>a582ddc32fc04817</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.765342</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.07493952321981423</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:08.752039Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>58e54f5015f64343</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>67987</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.520495</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.11065893442622954</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:10.234884Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>f2d0a0bd7e464ba9</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>67989</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.569339</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>-0.09052494557823132</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:11.230445Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>f1e61a5e54f347e0</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>68095</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.519652</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.14928162962962965</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:12.340375Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ42"/>
+  <autoFilter ref="A1:AJ48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ191"/>
+  <dimension ref="A1:AJ198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20236,8 +20236,722 @@
       <c r="AI191" s="2" t="inlineStr"/>
       <c r="AJ191" s="2" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>032df68f86d440d6</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>f1fe994de287718d3c0fe00feaf937f6ad521dd7146bd6199a6b119f5aadc7b4</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>0.528265</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.15789462962962963</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:19.019653Z</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
+      <c r="AG192" s="2" t="inlineStr"/>
+      <c r="AH192" s="2" t="inlineStr"/>
+      <c r="AI192" s="2" t="inlineStr"/>
+      <c r="AJ192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ff5d3c6cb0084561</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>f1fe994de287718d3c0fe00feaf937f6ad521dd7146bd6199a6b119f5aadc7b4</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>-0.07663969969969975</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:20.288436Z</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr"/>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
+      <c r="AG193" s="2" t="inlineStr"/>
+      <c r="AH193" s="2" t="inlineStr"/>
+      <c r="AI193" s="2" t="inlineStr"/>
+      <c r="AJ193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>26ce935b818243d1</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>f1fe994de287718d3c0fe00feaf937f6ad521dd7146bd6199a6b119f5aadc7b4</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:21.566885Z</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AG194" s="2" t="inlineStr"/>
+      <c r="AH194" s="2" t="inlineStr"/>
+      <c r="AI194" s="2" t="inlineStr"/>
+      <c r="AJ194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>7616c5f7285f4e22</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>0.528265</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>0.16855276978417266</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.352788Z</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
+      <c r="AG195" s="2" t="inlineStr"/>
+      <c r="AH195" s="2" t="inlineStr"/>
+      <c r="AI195" s="2" t="inlineStr"/>
+      <c r="AJ195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>9d561e446e4d4d58</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>-0.05745118210862621</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:23.433159Z</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
+      <c r="AG196" s="2" t="inlineStr"/>
+      <c r="AH196" s="2" t="inlineStr"/>
+      <c r="AI196" s="2" t="inlineStr"/>
+      <c r="AJ196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>f6d8f5c4bd5c4ca9</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.09863843192488264</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.642540Z</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
+      <c r="AG197" s="2" t="inlineStr"/>
+      <c r="AH197" s="2" t="inlineStr"/>
+      <c r="AI197" s="2" t="inlineStr"/>
+      <c r="AJ197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>6e667289fadc4a23</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>69954</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>0.685526</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>-0.014173699699699727</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.316942Z</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AG198" s="2" t="inlineStr"/>
+      <c r="AH198" s="2" t="inlineStr"/>
+      <c r="AI198" s="2" t="inlineStr"/>
+      <c r="AJ198" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ191"/>
+  <autoFilter ref="A1:AJ198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ198"/>
+  <dimension ref="A1:AJ208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20950,8 +20950,1028 @@
       <c r="AI198" s="2" t="inlineStr"/>
       <c r="AJ198" s="2" t="inlineStr"/>
     </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>da6e3641fce64b6c</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>d69696ee60884cdbbc02198278826e438fa3acb3c76bffb0930437b7d83a7650</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>0.528265</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr"/>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>0.16855276978417266</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:37.502496Z</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+      <c r="AE199" s="2" t="inlineStr"/>
+      <c r="AF199" s="2" t="inlineStr"/>
+      <c r="AG199" s="2" t="inlineStr"/>
+      <c r="AH199" s="2" t="inlineStr"/>
+      <c r="AI199" s="2" t="inlineStr"/>
+      <c r="AJ199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>7afae93511504965</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>d69696ee60884cdbbc02198278826e438fa3acb3c76bffb0930437b7d83a7650</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr"/>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>-0.05745118210862621</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:39.769187Z</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+      <c r="AB200" s="2" t="inlineStr"/>
+      <c r="AC200" s="2" t="inlineStr"/>
+      <c r="AD200" s="2" t="inlineStr"/>
+      <c r="AE200" s="2" t="inlineStr"/>
+      <c r="AF200" s="2" t="inlineStr"/>
+      <c r="AG200" s="2" t="inlineStr"/>
+      <c r="AH200" s="2" t="inlineStr"/>
+      <c r="AI200" s="2" t="inlineStr"/>
+      <c r="AJ200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>82ea232ee06f436b</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>d69696ee60884cdbbc02198278826e438fa3acb3c76bffb0930437b7d83a7650</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>0.09863843192488264</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:41.929766Z</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+      <c r="AB201" s="2" t="inlineStr"/>
+      <c r="AC201" s="2" t="inlineStr"/>
+      <c r="AD201" s="2" t="inlineStr"/>
+      <c r="AE201" s="2" t="inlineStr"/>
+      <c r="AF201" s="2" t="inlineStr"/>
+      <c r="AG201" s="2" t="inlineStr"/>
+      <c r="AH201" s="2" t="inlineStr"/>
+      <c r="AI201" s="2" t="inlineStr"/>
+      <c r="AJ201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>97e4d9b1b19d4b47</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>d69696ee60884cdbbc02198278826e438fa3acb3c76bffb0930437b7d83a7650</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>69954</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>0.685526</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr"/>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>-0.014173699699699727</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:45.262354Z</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+      <c r="AB202" s="2" t="inlineStr"/>
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="2" t="inlineStr"/>
+      <c r="AE202" s="2" t="inlineStr"/>
+      <c r="AF202" s="2" t="inlineStr"/>
+      <c r="AG202" s="2" t="inlineStr"/>
+      <c r="AH202" s="2" t="inlineStr"/>
+      <c r="AI202" s="2" t="inlineStr"/>
+      <c r="AJ202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>e7fa39aa7e55491b</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>aeca52ed5c92138baf9a32bd54c644f4cc5ff0cb6b6d88a1a4fea391ba441e5f</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>0.528265</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr"/>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>0.17861465034965035</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:06.061006Z</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
+      <c r="AG203" s="2" t="inlineStr"/>
+      <c r="AH203" s="2" t="inlineStr"/>
+      <c r="AI203" s="2" t="inlineStr"/>
+      <c r="AJ203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>d72ee04d48be4eaf</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>aeca52ed5c92138baf9a32bd54c644f4cc5ff0cb6b6d88a1a4fea391ba441e5f</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>-0.027289650349650363</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:07.197777Z</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
+      <c r="AG204" s="2" t="inlineStr"/>
+      <c r="AH204" s="2" t="inlineStr"/>
+      <c r="AI204" s="2" t="inlineStr"/>
+      <c r="AJ204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>f063f11cb01b4e07</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>aeca52ed5c92138baf9a32bd54c644f4cc5ff0cb6b6d88a1a4fea391ba441e5f</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.272042Z</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AG205" s="2" t="inlineStr"/>
+      <c r="AH205" s="2" t="inlineStr"/>
+      <c r="AI205" s="2" t="inlineStr"/>
+      <c r="AJ205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>651c6ab82aac4756</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>68481</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>0.528265</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.17861465034965035</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:40.372782Z</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr"/>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
+      <c r="AG206" s="2" t="inlineStr"/>
+      <c r="AH206" s="2" t="inlineStr"/>
+      <c r="AI206" s="2" t="inlineStr"/>
+      <c r="AJ206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>68da0794b16f4683</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>-0.027289650349650363</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:41.796927Z</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
+      <c r="AG207" s="2" t="inlineStr"/>
+      <c r="AH207" s="2" t="inlineStr"/>
+      <c r="AI207" s="2" t="inlineStr"/>
+      <c r="AJ207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>55efd86674664b3c</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr"/>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.943962Z</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+      <c r="AE208" s="2" t="inlineStr"/>
+      <c r="AF208" s="2" t="inlineStr"/>
+      <c r="AG208" s="2" t="inlineStr"/>
+      <c r="AH208" s="2" t="inlineStr"/>
+      <c r="AI208" s="2" t="inlineStr"/>
+      <c r="AJ208" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ198"/>
+  <autoFilter ref="A1:AJ208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ208"/>
+  <dimension ref="A1:AJ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -21750,14 +21750,34 @@
       <c r="W206" s="2" t="inlineStr"/>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y206" s="2" t="inlineStr"/>
-      <c r="Z206" s="2" t="inlineStr"/>
-      <c r="AA206" s="2" t="inlineStr"/>
-      <c r="AB206" s="2" t="inlineStr"/>
-      <c r="AC206" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z206" s="2" t="inlineStr">
+        <is>
+          <t>0.350000</t>
+        </is>
+      </c>
+      <c r="AA206" s="2" t="inlineStr">
+        <is>
+          <t>0.000350</t>
+        </is>
+      </c>
+      <c r="AB206" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:46.127304Z</t>
+        </is>
+      </c>
       <c r="AD206" s="2" t="inlineStr"/>
       <c r="AE206" s="2" t="inlineStr"/>
       <c r="AF206" s="2" t="inlineStr"/>
@@ -21970,8 +21990,2374 @@
       <c r="AI208" s="2" t="inlineStr"/>
       <c r="AJ208" s="2" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>3da38d17777948a7</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>4dd19640fd8669d65e0cf5399cede0ff0058dfe4bb6481bcbbc7e5d341d26579</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>0.62306</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr"/>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>-0.027289650349650363</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:18.537227Z</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr"/>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+      <c r="AE209" s="2" t="inlineStr"/>
+      <c r="AF209" s="2" t="inlineStr"/>
+      <c r="AG209" s="2" t="inlineStr"/>
+      <c r="AH209" s="2" t="inlineStr"/>
+      <c r="AI209" s="2" t="inlineStr"/>
+      <c r="AJ209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>4cc1ab51bbcc415e</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>4dd19640fd8669d65e0cf5399cede0ff0058dfe4bb6481bcbbc7e5d341d26579</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>0.568122</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr"/>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>0.10729250691244241</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:20.253708Z</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr"/>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr"/>
+      <c r="AB210" s="2" t="inlineStr"/>
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="2" t="inlineStr"/>
+      <c r="AE210" s="2" t="inlineStr"/>
+      <c r="AF210" s="2" t="inlineStr"/>
+      <c r="AG210" s="2" t="inlineStr"/>
+      <c r="AH210" s="2" t="inlineStr"/>
+      <c r="AI210" s="2" t="inlineStr"/>
+      <c r="AJ210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>b89a80d0b9414319</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>0.64657</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>0.026798136882129286</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:14.515679Z</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z211" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA211" s="2" t="inlineStr">
+        <is>
+          <t>0.010228</t>
+        </is>
+      </c>
+      <c r="AB211" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:59:59.184725Z</t>
+        </is>
+      </c>
+      <c r="AD211" s="2" t="inlineStr"/>
+      <c r="AE211" s="2" t="inlineStr"/>
+      <c r="AF211" s="2" t="inlineStr"/>
+      <c r="AG211" s="2" t="inlineStr"/>
+      <c r="AH211" s="2" t="inlineStr"/>
+      <c r="AI211" s="2" t="inlineStr"/>
+      <c r="AJ211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>d154c0c5fbe74857</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>0.574697</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr"/>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>0.1138675069124424</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:15.902210Z</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+      <c r="AB212" s="2" t="inlineStr"/>
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="2" t="inlineStr"/>
+      <c r="AE212" s="2" t="inlineStr"/>
+      <c r="AF212" s="2" t="inlineStr"/>
+      <c r="AG212" s="2" t="inlineStr"/>
+      <c r="AH212" s="2" t="inlineStr"/>
+      <c r="AI212" s="2" t="inlineStr"/>
+      <c r="AJ212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>c165eee8466b4938</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>b42115c33f33aabcc9de0f93a630372616064e7907433f1bdf7964ec917a67c7</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>0.574902</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>0.10541843192488265</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:16.186304Z</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+      <c r="AB213" s="2" t="inlineStr"/>
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="2" t="inlineStr"/>
+      <c r="AE213" s="2" t="inlineStr"/>
+      <c r="AF213" s="2" t="inlineStr"/>
+      <c r="AG213" s="2" t="inlineStr"/>
+      <c r="AH213" s="2" t="inlineStr"/>
+      <c r="AI213" s="2" t="inlineStr"/>
+      <c r="AJ213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>5ac870f93e1f4aeb</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>1cd85b2e2088b327e661d25667fdd01f350a091b1e11d3fbb8c1367cbe11fa21</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>0.575467</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>0.10598343192488258</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:39.371107Z</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr"/>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+      <c r="AB214" s="2" t="inlineStr"/>
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="2" t="inlineStr"/>
+      <c r="AE214" s="2" t="inlineStr"/>
+      <c r="AF214" s="2" t="inlineStr"/>
+      <c r="AG214" s="2" t="inlineStr"/>
+      <c r="AH214" s="2" t="inlineStr"/>
+      <c r="AI214" s="2" t="inlineStr"/>
+      <c r="AJ214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>76fd77013d3f4b48</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>ba67dd6aaae3eb83de1dbe1071b7a5eaa8213438dec9ededf1423df90efa991c</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>0.575339</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>0.10585543192488267</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:45.843691Z</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr"/>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
+      <c r="AB215" s="2" t="inlineStr"/>
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="2" t="inlineStr"/>
+      <c r="AE215" s="2" t="inlineStr"/>
+      <c r="AF215" s="2" t="inlineStr"/>
+      <c r="AG215" s="2" t="inlineStr"/>
+      <c r="AH215" s="2" t="inlineStr"/>
+      <c r="AI215" s="2" t="inlineStr"/>
+      <c r="AJ215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>99b0111d78ee41a5</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>0.575205</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr"/>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>0.12475454954954945</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:20.493480Z</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr"/>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
+      <c r="AB216" s="2" t="inlineStr"/>
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="2" t="inlineStr"/>
+      <c r="AE216" s="2" t="inlineStr"/>
+      <c r="AF216" s="2" t="inlineStr"/>
+      <c r="AG216" s="2" t="inlineStr"/>
+      <c r="AH216" s="2" t="inlineStr"/>
+      <c r="AI216" s="2" t="inlineStr"/>
+      <c r="AJ216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>4153a42cb3504bfd</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>0.669254</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>0.059879000000000016</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:24.538997Z</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr"/>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+      <c r="AB217" s="2" t="inlineStr"/>
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="2" t="inlineStr"/>
+      <c r="AE217" s="2" t="inlineStr"/>
+      <c r="AF217" s="2" t="inlineStr"/>
+      <c r="AG217" s="2" t="inlineStr"/>
+      <c r="AH217" s="2" t="inlineStr"/>
+      <c r="AI217" s="2" t="inlineStr"/>
+      <c r="AJ217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>e52f2a1cd65e4801</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>0.618991</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr"/>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>-0.02129676978417272</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:25.354268Z</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr"/>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr"/>
+      <c r="AB218" s="2" t="inlineStr"/>
+      <c r="AC218" s="2" t="inlineStr"/>
+      <c r="AD218" s="2" t="inlineStr"/>
+      <c r="AE218" s="2" t="inlineStr"/>
+      <c r="AF218" s="2" t="inlineStr"/>
+      <c r="AG218" s="2" t="inlineStr"/>
+      <c r="AH218" s="2" t="inlineStr"/>
+      <c r="AI218" s="2" t="inlineStr"/>
+      <c r="AJ218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>eaa88a77110e4c2f</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>0.702792</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr"/>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>0.312167</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:26.219958Z</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr"/>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr"/>
+      <c r="AB219" s="2" t="inlineStr"/>
+      <c r="AC219" s="2" t="inlineStr"/>
+      <c r="AD219" s="2" t="inlineStr"/>
+      <c r="AE219" s="2" t="inlineStr"/>
+      <c r="AF219" s="2" t="inlineStr"/>
+      <c r="AG219" s="2" t="inlineStr"/>
+      <c r="AH219" s="2" t="inlineStr"/>
+      <c r="AI219" s="2" t="inlineStr"/>
+      <c r="AJ219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>3f9ff74ce64f4681</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>0.536052</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr"/>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>-0.054111934426229524</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:26.981539Z</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr"/>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
+      <c r="AB220" s="2" t="inlineStr"/>
+      <c r="AC220" s="2" t="inlineStr"/>
+      <c r="AD220" s="2" t="inlineStr"/>
+      <c r="AE220" s="2" t="inlineStr"/>
+      <c r="AF220" s="2" t="inlineStr"/>
+      <c r="AG220" s="2" t="inlineStr"/>
+      <c r="AH220" s="2" t="inlineStr"/>
+      <c r="AI220" s="2" t="inlineStr"/>
+      <c r="AJ220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>c82cd28179364e20</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>0.550013</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr"/>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr"/>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>-0.14038947678018576</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:29.928145Z</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+      <c r="AB221" s="2" t="inlineStr"/>
+      <c r="AC221" s="2" t="inlineStr"/>
+      <c r="AD221" s="2" t="inlineStr"/>
+      <c r="AE221" s="2" t="inlineStr"/>
+      <c r="AF221" s="2" t="inlineStr"/>
+      <c r="AG221" s="2" t="inlineStr"/>
+      <c r="AH221" s="2" t="inlineStr"/>
+      <c r="AI221" s="2" t="inlineStr"/>
+      <c r="AJ221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>dbd8cb41377442d4</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>0.564054</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr"/>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>0.1936836296296297</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:30.958246Z</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
+      <c r="AB222" s="2" t="inlineStr"/>
+      <c r="AC222" s="2" t="inlineStr"/>
+      <c r="AD222" s="2" t="inlineStr"/>
+      <c r="AE222" s="2" t="inlineStr"/>
+      <c r="AF222" s="2" t="inlineStr"/>
+      <c r="AG222" s="2" t="inlineStr"/>
+      <c r="AH222" s="2" t="inlineStr"/>
+      <c r="AI222" s="2" t="inlineStr"/>
+      <c r="AJ222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>cd2a962eabf9494f</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>f4aa195b7766a10f558c7ae43fa4da36f27c6e5ce1ccf4b3c0ea975ff9acd811</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>0.626628</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr"/>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>0.17617754954954945</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:32.501687Z</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr"/>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr"/>
+      <c r="AB223" s="2" t="inlineStr"/>
+      <c r="AC223" s="2" t="inlineStr"/>
+      <c r="AD223" s="2" t="inlineStr"/>
+      <c r="AE223" s="2" t="inlineStr"/>
+      <c r="AF223" s="2" t="inlineStr"/>
+      <c r="AG223" s="2" t="inlineStr"/>
+      <c r="AH223" s="2" t="inlineStr"/>
+      <c r="AI223" s="2" t="inlineStr"/>
+      <c r="AJ223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>d0a131a2e77c4773</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>0.575198</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr"/>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>0.12474754954954947</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.028876Z</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr"/>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr"/>
+      <c r="AB224" s="2" t="inlineStr"/>
+      <c r="AC224" s="2" t="inlineStr"/>
+      <c r="AD224" s="2" t="inlineStr"/>
+      <c r="AE224" s="2" t="inlineStr"/>
+      <c r="AF224" s="2" t="inlineStr"/>
+      <c r="AG224" s="2" t="inlineStr"/>
+      <c r="AH224" s="2" t="inlineStr"/>
+      <c r="AI224" s="2" t="inlineStr"/>
+      <c r="AJ224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>17d5442629eb414c</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>0.669245</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr"/>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr"/>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>0.05986999999999998</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:14.218178Z</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr"/>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+      <c r="AB225" s="2" t="inlineStr"/>
+      <c r="AC225" s="2" t="inlineStr"/>
+      <c r="AD225" s="2" t="inlineStr"/>
+      <c r="AE225" s="2" t="inlineStr"/>
+      <c r="AF225" s="2" t="inlineStr"/>
+      <c r="AG225" s="2" t="inlineStr"/>
+      <c r="AH225" s="2" t="inlineStr"/>
+      <c r="AI225" s="2" t="inlineStr"/>
+      <c r="AJ225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>985f1cc7978744a8</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>0.618982</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr"/>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>-0.021305769784172646</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.077660Z</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr"/>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
+      <c r="AB226" s="2" t="inlineStr"/>
+      <c r="AC226" s="2" t="inlineStr"/>
+      <c r="AD226" s="2" t="inlineStr"/>
+      <c r="AE226" s="2" t="inlineStr"/>
+      <c r="AF226" s="2" t="inlineStr"/>
+      <c r="AG226" s="2" t="inlineStr"/>
+      <c r="AH226" s="2" t="inlineStr"/>
+      <c r="AI226" s="2" t="inlineStr"/>
+      <c r="AJ226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>97b69fa352894820</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>0.702781</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr"/>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr"/>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>0.312156</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.903165Z</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr"/>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
+      <c r="AB227" s="2" t="inlineStr"/>
+      <c r="AC227" s="2" t="inlineStr"/>
+      <c r="AD227" s="2" t="inlineStr"/>
+      <c r="AE227" s="2" t="inlineStr"/>
+      <c r="AF227" s="2" t="inlineStr"/>
+      <c r="AG227" s="2" t="inlineStr"/>
+      <c r="AH227" s="2" t="inlineStr"/>
+      <c r="AI227" s="2" t="inlineStr"/>
+      <c r="AJ227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>21eb2dd455264de1</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>0.536052</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr"/>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>-0.054111934426229524</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:16.712984Z</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr"/>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
+      <c r="AB228" s="2" t="inlineStr"/>
+      <c r="AC228" s="2" t="inlineStr"/>
+      <c r="AD228" s="2" t="inlineStr"/>
+      <c r="AE228" s="2" t="inlineStr"/>
+      <c r="AF228" s="2" t="inlineStr"/>
+      <c r="AG228" s="2" t="inlineStr"/>
+      <c r="AH228" s="2" t="inlineStr"/>
+      <c r="AI228" s="2" t="inlineStr"/>
+      <c r="AJ228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>0f671ddd95e442b4</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>0.550011</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr"/>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr"/>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>-0.10985294557823133</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:17.574738Z</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr"/>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+      <c r="AB229" s="2" t="inlineStr"/>
+      <c r="AC229" s="2" t="inlineStr"/>
+      <c r="AD229" s="2" t="inlineStr"/>
+      <c r="AE229" s="2" t="inlineStr"/>
+      <c r="AF229" s="2" t="inlineStr"/>
+      <c r="AG229" s="2" t="inlineStr"/>
+      <c r="AH229" s="2" t="inlineStr"/>
+      <c r="AI229" s="2" t="inlineStr"/>
+      <c r="AJ229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>d9029a2b5ea543ed</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>0.564051</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr"/>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>0.19368062962962962</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:18.444919Z</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr"/>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
+      <c r="AB230" s="2" t="inlineStr"/>
+      <c r="AC230" s="2" t="inlineStr"/>
+      <c r="AD230" s="2" t="inlineStr"/>
+      <c r="AE230" s="2" t="inlineStr"/>
+      <c r="AF230" s="2" t="inlineStr"/>
+      <c r="AG230" s="2" t="inlineStr"/>
+      <c r="AH230" s="2" t="inlineStr"/>
+      <c r="AI230" s="2" t="inlineStr"/>
+      <c r="AJ230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>6dd577af808442d2</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>0.626622</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr"/>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr"/>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>0.1761715495495495</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.044205Z</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr"/>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
+      <c r="AB231" s="2" t="inlineStr"/>
+      <c r="AC231" s="2" t="inlineStr"/>
+      <c r="AD231" s="2" t="inlineStr"/>
+      <c r="AE231" s="2" t="inlineStr"/>
+      <c r="AF231" s="2" t="inlineStr"/>
+      <c r="AG231" s="2" t="inlineStr"/>
+      <c r="AH231" s="2" t="inlineStr"/>
+      <c r="AI231" s="2" t="inlineStr"/>
+      <c r="AJ231" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ208"/>
+  <autoFilter ref="A1:AJ231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ231"/>
+  <dimension ref="A1:AJ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -23626,14 +23626,34 @@
       <c r="W224" s="2" t="inlineStr"/>
       <c r="X224" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y224" s="2" t="inlineStr"/>
-      <c r="Z224" s="2" t="inlineStr"/>
-      <c r="AA224" s="2" t="inlineStr"/>
-      <c r="AB224" s="2" t="inlineStr"/>
-      <c r="AC224" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>0.450000</t>
+        </is>
+      </c>
+      <c r="AA224" s="2" t="inlineStr">
+        <is>
+          <t>-0.000450</t>
+        </is>
+      </c>
+      <c r="AB224" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:50.284204Z</t>
+        </is>
+      </c>
       <c r="AD224" s="2" t="inlineStr"/>
       <c r="AE224" s="2" t="inlineStr"/>
       <c r="AF224" s="2" t="inlineStr"/>
@@ -24356,8 +24376,2456 @@
       <c r="AI231" s="2" t="inlineStr"/>
       <c r="AJ231" s="2" t="inlineStr"/>
     </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>563aabea7fba4f5e</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>69955</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>0.69065</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr"/>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr"/>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>-0.00904969969969971</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:16.780739Z</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr"/>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
+      <c r="AB232" s="2" t="inlineStr"/>
+      <c r="AC232" s="2" t="inlineStr"/>
+      <c r="AD232" s="2" t="inlineStr"/>
+      <c r="AE232" s="2" t="inlineStr"/>
+      <c r="AF232" s="2" t="inlineStr"/>
+      <c r="AG232" s="2" t="inlineStr"/>
+      <c r="AH232" s="2" t="inlineStr"/>
+      <c r="AI232" s="2" t="inlineStr"/>
+      <c r="AJ232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>60213d509840492c</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>0.668954</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="2" t="inlineStr"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr"/>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>0.05957900000000005</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:17.314063Z</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr"/>
+      <c r="X233" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr"/>
+      <c r="AA233" s="2" t="inlineStr"/>
+      <c r="AB233" s="2" t="inlineStr"/>
+      <c r="AC233" s="2" t="inlineStr"/>
+      <c r="AD233" s="2" t="inlineStr"/>
+      <c r="AE233" s="2" t="inlineStr"/>
+      <c r="AF233" s="2" t="inlineStr"/>
+      <c r="AG233" s="2" t="inlineStr"/>
+      <c r="AH233" s="2" t="inlineStr"/>
+      <c r="AI233" s="2" t="inlineStr"/>
+      <c r="AJ233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>25b1958bd6094e52</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>0.618728</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr"/>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr"/>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>-0.031621650349650365</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:18.531565Z</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr"/>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr"/>
+      <c r="AA234" s="2" t="inlineStr"/>
+      <c r="AB234" s="2" t="inlineStr"/>
+      <c r="AC234" s="2" t="inlineStr"/>
+      <c r="AD234" s="2" t="inlineStr"/>
+      <c r="AE234" s="2" t="inlineStr"/>
+      <c r="AF234" s="2" t="inlineStr"/>
+      <c r="AG234" s="2" t="inlineStr"/>
+      <c r="AH234" s="2" t="inlineStr"/>
+      <c r="AI234" s="2" t="inlineStr"/>
+      <c r="AJ234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>f3f97427fbf5439a</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>0.702279</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr"/>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr"/>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>0.311654</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:19.113124Z</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr"/>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr"/>
+      <c r="AA235" s="2" t="inlineStr"/>
+      <c r="AB235" s="2" t="inlineStr"/>
+      <c r="AC235" s="2" t="inlineStr"/>
+      <c r="AD235" s="2" t="inlineStr"/>
+      <c r="AE235" s="2" t="inlineStr"/>
+      <c r="AF235" s="2" t="inlineStr"/>
+      <c r="AG235" s="2" t="inlineStr"/>
+      <c r="AH235" s="2" t="inlineStr"/>
+      <c r="AI235" s="2" t="inlineStr"/>
+      <c r="AJ235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>dd2a28210baa4983</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>0.53623</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr"/>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr"/>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>-0.0436019327731092</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:19.669618Z</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr"/>
+      <c r="AA236" s="2" t="inlineStr"/>
+      <c r="AB236" s="2" t="inlineStr"/>
+      <c r="AC236" s="2" t="inlineStr"/>
+      <c r="AD236" s="2" t="inlineStr"/>
+      <c r="AE236" s="2" t="inlineStr"/>
+      <c r="AF236" s="2" t="inlineStr"/>
+      <c r="AG236" s="2" t="inlineStr"/>
+      <c r="AH236" s="2" t="inlineStr"/>
+      <c r="AI236" s="2" t="inlineStr"/>
+      <c r="AJ236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>bf48bd6c60894a96</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>0.550055</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr"/>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>-0.09023276978417272</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:20.229196Z</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr"/>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr"/>
+      <c r="AB237" s="2" t="inlineStr"/>
+      <c r="AC237" s="2" t="inlineStr"/>
+      <c r="AD237" s="2" t="inlineStr"/>
+      <c r="AE237" s="2" t="inlineStr"/>
+      <c r="AF237" s="2" t="inlineStr"/>
+      <c r="AG237" s="2" t="inlineStr"/>
+      <c r="AH237" s="2" t="inlineStr"/>
+      <c r="AI237" s="2" t="inlineStr"/>
+      <c r="AJ237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2d79aa83ef9b4e35</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>0.563849</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr"/>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr"/>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>0.1934786296296297</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:21.604476Z</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr"/>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr"/>
+      <c r="AB238" s="2" t="inlineStr"/>
+      <c r="AC238" s="2" t="inlineStr"/>
+      <c r="AD238" s="2" t="inlineStr"/>
+      <c r="AE238" s="2" t="inlineStr"/>
+      <c r="AF238" s="2" t="inlineStr"/>
+      <c r="AG238" s="2" t="inlineStr"/>
+      <c r="AH238" s="2" t="inlineStr"/>
+      <c r="AI238" s="2" t="inlineStr"/>
+      <c r="AJ238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>fa37b482ef204173</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>07fa8b76447a0fc0d62d7da1c6700586354c51a9fe2df908638056e714755678</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>0.626211</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr"/>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr"/>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>0.1856823656387665</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:22.297943Z</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr"/>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
+      <c r="AB239" s="2" t="inlineStr"/>
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="2" t="inlineStr"/>
+      <c r="AE239" s="2" t="inlineStr"/>
+      <c r="AF239" s="2" t="inlineStr"/>
+      <c r="AG239" s="2" t="inlineStr"/>
+      <c r="AH239" s="2" t="inlineStr"/>
+      <c r="AI239" s="2" t="inlineStr"/>
+      <c r="AJ239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>b11e0abd98424e02</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>69955</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>0.690629</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr"/>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr"/>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>-0.009070699699699647</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:30.710279Z</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr"/>
+      <c r="W240" s="2" t="inlineStr"/>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr"/>
+      <c r="AB240" s="2" t="inlineStr"/>
+      <c r="AC240" s="2" t="inlineStr"/>
+      <c r="AD240" s="2" t="inlineStr"/>
+      <c r="AE240" s="2" t="inlineStr"/>
+      <c r="AF240" s="2" t="inlineStr"/>
+      <c r="AG240" s="2" t="inlineStr"/>
+      <c r="AH240" s="2" t="inlineStr"/>
+      <c r="AI240" s="2" t="inlineStr"/>
+      <c r="AJ240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>e42b27b82fc2403f</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>0.668936</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr"/>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr"/>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>0.059560999999999975</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:31.989777Z</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr"/>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
+      <c r="AB241" s="2" t="inlineStr"/>
+      <c r="AC241" s="2" t="inlineStr"/>
+      <c r="AD241" s="2" t="inlineStr"/>
+      <c r="AE241" s="2" t="inlineStr"/>
+      <c r="AF241" s="2" t="inlineStr"/>
+      <c r="AG241" s="2" t="inlineStr"/>
+      <c r="AH241" s="2" t="inlineStr"/>
+      <c r="AI241" s="2" t="inlineStr"/>
+      <c r="AJ241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>6a2651a439a64ba5</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>0.618708</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr"/>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr"/>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>-0.031641650349650274</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:32.649396Z</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr"/>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr"/>
+      <c r="AB242" s="2" t="inlineStr"/>
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="2" t="inlineStr"/>
+      <c r="AE242" s="2" t="inlineStr"/>
+      <c r="AF242" s="2" t="inlineStr"/>
+      <c r="AG242" s="2" t="inlineStr"/>
+      <c r="AH242" s="2" t="inlineStr"/>
+      <c r="AI242" s="2" t="inlineStr"/>
+      <c r="AJ242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>b35f2555870f48b9</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>0.702255</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr"/>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr"/>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>0.31162999999999996</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:33.130398Z</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr"/>
+      <c r="W243" s="2" t="inlineStr"/>
+      <c r="X243" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
+      <c r="AB243" s="2" t="inlineStr"/>
+      <c r="AC243" s="2" t="inlineStr"/>
+      <c r="AD243" s="2" t="inlineStr"/>
+      <c r="AE243" s="2" t="inlineStr"/>
+      <c r="AF243" s="2" t="inlineStr"/>
+      <c r="AG243" s="2" t="inlineStr"/>
+      <c r="AH243" s="2" t="inlineStr"/>
+      <c r="AI243" s="2" t="inlineStr"/>
+      <c r="AJ243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>a536ee751ff14ff7</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>0.536229</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr"/>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr"/>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>-0.043602932773109226</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:33.960664Z</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr"/>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr"/>
+      <c r="AB244" s="2" t="inlineStr"/>
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="2" t="inlineStr"/>
+      <c r="AE244" s="2" t="inlineStr"/>
+      <c r="AF244" s="2" t="inlineStr"/>
+      <c r="AG244" s="2" t="inlineStr"/>
+      <c r="AH244" s="2" t="inlineStr"/>
+      <c r="AI244" s="2" t="inlineStr"/>
+      <c r="AJ244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>7a4130588b104ee5</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>0.550051</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr"/>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr"/>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>-0.09023676978417272</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:34.554942Z</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr"/>
+      <c r="W245" s="2" t="inlineStr"/>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr"/>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+      <c r="AE245" s="2" t="inlineStr"/>
+      <c r="AF245" s="2" t="inlineStr"/>
+      <c r="AG245" s="2" t="inlineStr"/>
+      <c r="AH245" s="2" t="inlineStr"/>
+      <c r="AI245" s="2" t="inlineStr"/>
+      <c r="AJ245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>961f70ae604c4415</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>0.563844</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr"/>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr"/>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>0.19347362962962966</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:35.676356Z</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr"/>
+      <c r="X246" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+      <c r="AB246" s="2" t="inlineStr"/>
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="2" t="inlineStr"/>
+      <c r="AE246" s="2" t="inlineStr"/>
+      <c r="AF246" s="2" t="inlineStr"/>
+      <c r="AG246" s="2" t="inlineStr"/>
+      <c r="AH246" s="2" t="inlineStr"/>
+      <c r="AI246" s="2" t="inlineStr"/>
+      <c r="AJ246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>0159bdf2195740d9</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>c739ead3892aeecfdd77bbf546cd551c3533fd6bfc01697bdac06d1f44ae0c34</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>0.626197</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr"/>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr"/>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>0.18566836563876654</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:36.643764Z</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr"/>
+      <c r="W247" s="2" t="inlineStr"/>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
+      <c r="AB247" s="2" t="inlineStr"/>
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="2" t="inlineStr"/>
+      <c r="AE247" s="2" t="inlineStr"/>
+      <c r="AF247" s="2" t="inlineStr"/>
+      <c r="AG247" s="2" t="inlineStr"/>
+      <c r="AH247" s="2" t="inlineStr"/>
+      <c r="AI247" s="2" t="inlineStr"/>
+      <c r="AJ247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>8bdf3f894d5446bb</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>69955</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>0.689698</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr"/>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr"/>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>-0.0007044767801857033</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:10.002030Z</t>
+        </is>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr"/>
+      <c r="X248" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y248" s="2" t="inlineStr"/>
+      <c r="Z248" s="2" t="inlineStr"/>
+      <c r="AA248" s="2" t="inlineStr"/>
+      <c r="AB248" s="2" t="inlineStr"/>
+      <c r="AC248" s="2" t="inlineStr"/>
+      <c r="AD248" s="2" t="inlineStr"/>
+      <c r="AE248" s="2" t="inlineStr"/>
+      <c r="AF248" s="2" t="inlineStr"/>
+      <c r="AG248" s="2" t="inlineStr"/>
+      <c r="AH248" s="2" t="inlineStr"/>
+      <c r="AI248" s="2" t="inlineStr"/>
+      <c r="AJ248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>ea99803396f545b9</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>0.667906</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr"/>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr"/>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>0.058531</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:10.639279Z</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr"/>
+      <c r="X249" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr"/>
+      <c r="AA249" s="2" t="inlineStr"/>
+      <c r="AB249" s="2" t="inlineStr"/>
+      <c r="AC249" s="2" t="inlineStr"/>
+      <c r="AD249" s="2" t="inlineStr"/>
+      <c r="AE249" s="2" t="inlineStr"/>
+      <c r="AF249" s="2" t="inlineStr"/>
+      <c r="AG249" s="2" t="inlineStr"/>
+      <c r="AH249" s="2" t="inlineStr"/>
+      <c r="AI249" s="2" t="inlineStr"/>
+      <c r="AJ249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>ebeaf9b5c6654f19</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>0.618449</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr"/>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="inlineStr"/>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>-0.031900650349650284</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:11.184348Z</t>
+        </is>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr"/>
+      <c r="W250" s="2" t="inlineStr"/>
+      <c r="X250" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y250" s="2" t="inlineStr"/>
+      <c r="Z250" s="2" t="inlineStr"/>
+      <c r="AA250" s="2" t="inlineStr"/>
+      <c r="AB250" s="2" t="inlineStr"/>
+      <c r="AC250" s="2" t="inlineStr"/>
+      <c r="AD250" s="2" t="inlineStr"/>
+      <c r="AE250" s="2" t="inlineStr"/>
+      <c r="AF250" s="2" t="inlineStr"/>
+      <c r="AG250" s="2" t="inlineStr"/>
+      <c r="AH250" s="2" t="inlineStr"/>
+      <c r="AI250" s="2" t="inlineStr"/>
+      <c r="AJ250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>4384fcce466f4dd2</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>0.701767</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr"/>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr"/>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>0.31114200000000003</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:11.760518Z</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr"/>
+      <c r="W251" s="2" t="inlineStr"/>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y251" s="2" t="inlineStr"/>
+      <c r="Z251" s="2" t="inlineStr"/>
+      <c r="AA251" s="2" t="inlineStr"/>
+      <c r="AB251" s="2" t="inlineStr"/>
+      <c r="AC251" s="2" t="inlineStr"/>
+      <c r="AD251" s="2" t="inlineStr"/>
+      <c r="AE251" s="2" t="inlineStr"/>
+      <c r="AF251" s="2" t="inlineStr"/>
+      <c r="AG251" s="2" t="inlineStr"/>
+      <c r="AH251" s="2" t="inlineStr"/>
+      <c r="AI251" s="2" t="inlineStr"/>
+      <c r="AJ251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>e9c7ea2bd4454f77</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>0.535831</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr"/>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr"/>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>-0.044000932773109236</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:12.281637Z</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr"/>
+      <c r="W252" s="2" t="inlineStr"/>
+      <c r="X252" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y252" s="2" t="inlineStr"/>
+      <c r="Z252" s="2" t="inlineStr"/>
+      <c r="AA252" s="2" t="inlineStr"/>
+      <c r="AB252" s="2" t="inlineStr"/>
+      <c r="AC252" s="2" t="inlineStr"/>
+      <c r="AD252" s="2" t="inlineStr"/>
+      <c r="AE252" s="2" t="inlineStr"/>
+      <c r="AF252" s="2" t="inlineStr"/>
+      <c r="AG252" s="2" t="inlineStr"/>
+      <c r="AH252" s="2" t="inlineStr"/>
+      <c r="AI252" s="2" t="inlineStr"/>
+      <c r="AJ252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>7a4a0f8456c14dd7</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>0.54962</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr"/>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr"/>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>-0.09066776978417268</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:12.754904Z</t>
+        </is>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr"/>
+      <c r="W253" s="2" t="inlineStr"/>
+      <c r="X253" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y253" s="2" t="inlineStr"/>
+      <c r="Z253" s="2" t="inlineStr"/>
+      <c r="AA253" s="2" t="inlineStr"/>
+      <c r="AB253" s="2" t="inlineStr"/>
+      <c r="AC253" s="2" t="inlineStr"/>
+      <c r="AD253" s="2" t="inlineStr"/>
+      <c r="AE253" s="2" t="inlineStr"/>
+      <c r="AF253" s="2" t="inlineStr"/>
+      <c r="AG253" s="2" t="inlineStr"/>
+      <c r="AH253" s="2" t="inlineStr"/>
+      <c r="AI253" s="2" t="inlineStr"/>
+      <c r="AJ253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>64768defe5324c84</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>0.563896</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr"/>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr"/>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>0.1935256296296296</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:13.229270Z</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr"/>
+      <c r="W254" s="2" t="inlineStr"/>
+      <c r="X254" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y254" s="2" t="inlineStr"/>
+      <c r="Z254" s="2" t="inlineStr"/>
+      <c r="AA254" s="2" t="inlineStr"/>
+      <c r="AB254" s="2" t="inlineStr"/>
+      <c r="AC254" s="2" t="inlineStr"/>
+      <c r="AD254" s="2" t="inlineStr"/>
+      <c r="AE254" s="2" t="inlineStr"/>
+      <c r="AF254" s="2" t="inlineStr"/>
+      <c r="AG254" s="2" t="inlineStr"/>
+      <c r="AH254" s="2" t="inlineStr"/>
+      <c r="AI254" s="2" t="inlineStr"/>
+      <c r="AJ254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>846a5f7336ee4c3a</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>0.625458</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr"/>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr"/>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>0.2052899327731092</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:14.786413Z</t>
+        </is>
+      </c>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr"/>
+      <c r="X255" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y255" s="2" t="inlineStr"/>
+      <c r="Z255" s="2" t="inlineStr"/>
+      <c r="AA255" s="2" t="inlineStr"/>
+      <c r="AB255" s="2" t="inlineStr"/>
+      <c r="AC255" s="2" t="inlineStr"/>
+      <c r="AD255" s="2" t="inlineStr"/>
+      <c r="AE255" s="2" t="inlineStr"/>
+      <c r="AF255" s="2" t="inlineStr"/>
+      <c r="AG255" s="2" t="inlineStr"/>
+      <c r="AH255" s="2" t="inlineStr"/>
+      <c r="AI255" s="2" t="inlineStr"/>
+      <c r="AJ255" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ231"/>
+  <autoFilter ref="A1:AJ255"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ255"/>
+  <dimension ref="A1:AJ304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -26824,8 +26824,5158 @@
       <c r="AI255" s="2" t="inlineStr"/>
       <c r="AJ255" s="2" t="inlineStr"/>
     </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>72ca10eaf7df4e68</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>69955</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>0.689085</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr"/>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr"/>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>0.02922105442176859</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:41.254236Z</t>
+        </is>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
+      <c r="W256" s="2" t="inlineStr"/>
+      <c r="X256" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y256" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z256" s="2" t="inlineStr">
+        <is>
+          <t>0.650000</t>
+        </is>
+      </c>
+      <c r="AA256" s="2" t="inlineStr">
+        <is>
+          <t>-0.009864</t>
+        </is>
+      </c>
+      <c r="AB256" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:20.424448Z</t>
+        </is>
+      </c>
+      <c r="AD256" s="2" t="inlineStr"/>
+      <c r="AE256" s="2" t="inlineStr"/>
+      <c r="AF256" s="2" t="inlineStr"/>
+      <c r="AG256" s="2" t="inlineStr"/>
+      <c r="AH256" s="2" t="inlineStr"/>
+      <c r="AI256" s="2" t="inlineStr"/>
+      <c r="AJ256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>f7d9ca19ab704bd3</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>0.667348</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr"/>
+      <c r="N257" s="2" t="inlineStr"/>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr"/>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>0.05797300000000005</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:41.772695Z</t>
+        </is>
+      </c>
+      <c r="S257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr"/>
+      <c r="W257" s="2" t="inlineStr"/>
+      <c r="X257" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr"/>
+      <c r="AA257" s="2" t="inlineStr"/>
+      <c r="AB257" s="2" t="inlineStr"/>
+      <c r="AC257" s="2" t="inlineStr"/>
+      <c r="AD257" s="2" t="inlineStr"/>
+      <c r="AE257" s="2" t="inlineStr"/>
+      <c r="AF257" s="2" t="inlineStr"/>
+      <c r="AG257" s="2" t="inlineStr"/>
+      <c r="AH257" s="2" t="inlineStr"/>
+      <c r="AI257" s="2" t="inlineStr"/>
+      <c r="AJ257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>1297ba220e4146b2</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>0.618299</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr"/>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr"/>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>-0.03205065034965027</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:42.284649Z</t>
+        </is>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr"/>
+      <c r="W258" s="2" t="inlineStr"/>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr"/>
+      <c r="AB258" s="2" t="inlineStr"/>
+      <c r="AC258" s="2" t="inlineStr"/>
+      <c r="AD258" s="2" t="inlineStr"/>
+      <c r="AE258" s="2" t="inlineStr"/>
+      <c r="AF258" s="2" t="inlineStr"/>
+      <c r="AG258" s="2" t="inlineStr"/>
+      <c r="AH258" s="2" t="inlineStr"/>
+      <c r="AI258" s="2" t="inlineStr"/>
+      <c r="AJ258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>f4b223d75d4b4059</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>0.70126</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr"/>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr"/>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>0.2914239344262295</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:42.864876Z</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr"/>
+      <c r="W259" s="2" t="inlineStr"/>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr"/>
+      <c r="Z259" s="2" t="inlineStr"/>
+      <c r="AA259" s="2" t="inlineStr"/>
+      <c r="AB259" s="2" t="inlineStr"/>
+      <c r="AC259" s="2" t="inlineStr"/>
+      <c r="AD259" s="2" t="inlineStr"/>
+      <c r="AE259" s="2" t="inlineStr"/>
+      <c r="AF259" s="2" t="inlineStr"/>
+      <c r="AG259" s="2" t="inlineStr"/>
+      <c r="AH259" s="2" t="inlineStr"/>
+      <c r="AI259" s="2" t="inlineStr"/>
+      <c r="AJ259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>76ca7339939e41d5</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>0.548163</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr"/>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr"/>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>-0.031668932773109226</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:43.346753Z</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr"/>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr"/>
+      <c r="AA260" s="2" t="inlineStr"/>
+      <c r="AB260" s="2" t="inlineStr"/>
+      <c r="AC260" s="2" t="inlineStr"/>
+      <c r="AD260" s="2" t="inlineStr"/>
+      <c r="AE260" s="2" t="inlineStr"/>
+      <c r="AF260" s="2" t="inlineStr"/>
+      <c r="AG260" s="2" t="inlineStr"/>
+      <c r="AH260" s="2" t="inlineStr"/>
+      <c r="AI260" s="2" t="inlineStr"/>
+      <c r="AJ260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>edb0fe9d83094c28</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>0.548944</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr"/>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr"/>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>-0.10140565034965032</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:43.947678Z</t>
+        </is>
+      </c>
+      <c r="S261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr"/>
+      <c r="X261" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr"/>
+      <c r="AB261" s="2" t="inlineStr"/>
+      <c r="AC261" s="2" t="inlineStr"/>
+      <c r="AD261" s="2" t="inlineStr"/>
+      <c r="AE261" s="2" t="inlineStr"/>
+      <c r="AF261" s="2" t="inlineStr"/>
+      <c r="AG261" s="2" t="inlineStr"/>
+      <c r="AH261" s="2" t="inlineStr"/>
+      <c r="AI261" s="2" t="inlineStr"/>
+      <c r="AJ261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>80de8d2305d1401f</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>0.563864</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr"/>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr"/>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>0.19349362962962968</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:44.459947Z</t>
+        </is>
+      </c>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr"/>
+      <c r="W262" s="2" t="inlineStr"/>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr"/>
+      <c r="AA262" s="2" t="inlineStr"/>
+      <c r="AB262" s="2" t="inlineStr"/>
+      <c r="AC262" s="2" t="inlineStr"/>
+      <c r="AD262" s="2" t="inlineStr"/>
+      <c r="AE262" s="2" t="inlineStr"/>
+      <c r="AF262" s="2" t="inlineStr"/>
+      <c r="AG262" s="2" t="inlineStr"/>
+      <c r="AH262" s="2" t="inlineStr"/>
+      <c r="AI262" s="2" t="inlineStr"/>
+      <c r="AJ262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>8feea088aa6d4633</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>99605999cbefc3e4318aa2d50dc2b92c9ca2bafd08c79807b93ccfd4969eebcd</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>0.624973</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr"/>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr"/>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>0.18444436563876654</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:45.562455Z</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
+      <c r="W263" s="2" t="inlineStr"/>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr"/>
+      <c r="AA263" s="2" t="inlineStr"/>
+      <c r="AB263" s="2" t="inlineStr"/>
+      <c r="AC263" s="2" t="inlineStr"/>
+      <c r="AD263" s="2" t="inlineStr"/>
+      <c r="AE263" s="2" t="inlineStr"/>
+      <c r="AF263" s="2" t="inlineStr"/>
+      <c r="AG263" s="2" t="inlineStr"/>
+      <c r="AH263" s="2" t="inlineStr"/>
+      <c r="AI263" s="2" t="inlineStr"/>
+      <c r="AJ263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>9cf0ada964364941</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>0.655255</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr"/>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr"/>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>0.03548313688212934</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:47.234875Z</t>
+        </is>
+      </c>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr"/>
+      <c r="X264" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y264" s="2" t="inlineStr"/>
+      <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr"/>
+      <c r="AB264" s="2" t="inlineStr"/>
+      <c r="AC264" s="2" t="inlineStr"/>
+      <c r="AD264" s="2" t="inlineStr"/>
+      <c r="AE264" s="2" t="inlineStr"/>
+      <c r="AF264" s="2" t="inlineStr"/>
+      <c r="AG264" s="2" t="inlineStr"/>
+      <c r="AH264" s="2" t="inlineStr"/>
+      <c r="AI264" s="2" t="inlineStr"/>
+      <c r="AJ264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>fb32ccbda5af4312</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>0.619466</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr"/>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr"/>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>-0.020821769784172717</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:47.938867Z</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr"/>
+      <c r="W265" s="2" t="inlineStr"/>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr"/>
+      <c r="AB265" s="2" t="inlineStr"/>
+      <c r="AC265" s="2" t="inlineStr"/>
+      <c r="AD265" s="2" t="inlineStr"/>
+      <c r="AE265" s="2" t="inlineStr"/>
+      <c r="AF265" s="2" t="inlineStr"/>
+      <c r="AG265" s="2" t="inlineStr"/>
+      <c r="AH265" s="2" t="inlineStr"/>
+      <c r="AI265" s="2" t="inlineStr"/>
+      <c r="AJ265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>31a2a07c94d84e3b</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>0.552344</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr"/>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr"/>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>-0.007127365638766592</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:48.566937Z</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr"/>
+      <c r="W266" s="2" t="inlineStr"/>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr"/>
+      <c r="AB266" s="2" t="inlineStr"/>
+      <c r="AC266" s="2" t="inlineStr"/>
+      <c r="AD266" s="2" t="inlineStr"/>
+      <c r="AE266" s="2" t="inlineStr"/>
+      <c r="AF266" s="2" t="inlineStr"/>
+      <c r="AG266" s="2" t="inlineStr"/>
+      <c r="AH266" s="2" t="inlineStr"/>
+      <c r="AI266" s="2" t="inlineStr"/>
+      <c r="AJ266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>56159b21b6e3439a</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>0.537512</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr"/>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr"/>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>-0.09211762962962955</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:49.143366Z</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr"/>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr"/>
+      <c r="AB267" s="2" t="inlineStr"/>
+      <c r="AC267" s="2" t="inlineStr"/>
+      <c r="AD267" s="2" t="inlineStr"/>
+      <c r="AE267" s="2" t="inlineStr"/>
+      <c r="AF267" s="2" t="inlineStr"/>
+      <c r="AG267" s="2" t="inlineStr"/>
+      <c r="AH267" s="2" t="inlineStr"/>
+      <c r="AI267" s="2" t="inlineStr"/>
+      <c r="AJ267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>1ebed1c8f0fa423a</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>0.695963</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr"/>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr"/>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>0.27579493277310924</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:49.787877Z</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr"/>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr"/>
+      <c r="AB268" s="2" t="inlineStr"/>
+      <c r="AC268" s="2" t="inlineStr"/>
+      <c r="AD268" s="2" t="inlineStr"/>
+      <c r="AE268" s="2" t="inlineStr"/>
+      <c r="AF268" s="2" t="inlineStr"/>
+      <c r="AG268" s="2" t="inlineStr"/>
+      <c r="AH268" s="2" t="inlineStr"/>
+      <c r="AI268" s="2" t="inlineStr"/>
+      <c r="AJ268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>4d741fdd630b4427</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>0.563078</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr"/>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr"/>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>0.20336576978417265</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:50.556034Z</t>
+        </is>
+      </c>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr"/>
+      <c r="W269" s="2" t="inlineStr"/>
+      <c r="X269" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr"/>
+      <c r="AB269" s="2" t="inlineStr"/>
+      <c r="AC269" s="2" t="inlineStr"/>
+      <c r="AD269" s="2" t="inlineStr"/>
+      <c r="AE269" s="2" t="inlineStr"/>
+      <c r="AF269" s="2" t="inlineStr"/>
+      <c r="AG269" s="2" t="inlineStr"/>
+      <c r="AH269" s="2" t="inlineStr"/>
+      <c r="AI269" s="2" t="inlineStr"/>
+      <c r="AJ269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>e8b9fe6c5f4845e3</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>1cd11f8919d6b9c0dff1662549efd58ecfefd674e45fe50ab9d398907f8f17de</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>0.615776</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr"/>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr"/>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>0.17524736563876653</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:51.720995Z</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr"/>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr"/>
+      <c r="AA270" s="2" t="inlineStr"/>
+      <c r="AB270" s="2" t="inlineStr"/>
+      <c r="AC270" s="2" t="inlineStr"/>
+      <c r="AD270" s="2" t="inlineStr"/>
+      <c r="AE270" s="2" t="inlineStr"/>
+      <c r="AF270" s="2" t="inlineStr"/>
+      <c r="AG270" s="2" t="inlineStr"/>
+      <c r="AH270" s="2" t="inlineStr"/>
+      <c r="AI270" s="2" t="inlineStr"/>
+      <c r="AJ270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2b0bf0b61a8b4717</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>0.655109</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr"/>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr"/>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>0.025479370370370513</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.545519Z</t>
+        </is>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr"/>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y271" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z271" s="2" t="inlineStr"/>
+      <c r="AA271" s="2" t="inlineStr"/>
+      <c r="AB271" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:45.836253Z</t>
+        </is>
+      </c>
+      <c r="AD271" s="2" t="inlineStr"/>
+      <c r="AE271" s="2" t="inlineStr"/>
+      <c r="AF271" s="2" t="inlineStr"/>
+      <c r="AG271" s="2" t="inlineStr"/>
+      <c r="AH271" s="2" t="inlineStr"/>
+      <c r="AI271" s="2" t="inlineStr"/>
+      <c r="AJ271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>914bf654b3cc4c41</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>70595</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>0.619297</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr"/>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr"/>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>-0.010332629629629553</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.130397Z</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="2" t="inlineStr"/>
+      <c r="W272" s="2" t="inlineStr"/>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr"/>
+      <c r="AB272" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:47.520578Z</t>
+        </is>
+      </c>
+      <c r="AD272" s="2" t="inlineStr"/>
+      <c r="AE272" s="2" t="inlineStr"/>
+      <c r="AF272" s="2" t="inlineStr"/>
+      <c r="AG272" s="2" t="inlineStr"/>
+      <c r="AH272" s="2" t="inlineStr"/>
+      <c r="AI272" s="2" t="inlineStr"/>
+      <c r="AJ272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>f96599fbd01a4402</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>0.55231</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr"/>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr"/>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>0.033079230769230805</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.602756Z</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr"/>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z273" s="2" t="inlineStr"/>
+      <c r="AA273" s="2" t="inlineStr"/>
+      <c r="AB273" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:49.198134Z</t>
+        </is>
+      </c>
+      <c r="AD273" s="2" t="inlineStr"/>
+      <c r="AE273" s="2" t="inlineStr"/>
+      <c r="AF273" s="2" t="inlineStr"/>
+      <c r="AG273" s="2" t="inlineStr"/>
+      <c r="AH273" s="2" t="inlineStr"/>
+      <c r="AI273" s="2" t="inlineStr"/>
+      <c r="AJ273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>0f2e38be119d4e0a</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>0.537492</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr"/>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr"/>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>-0.09213762962962957</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.090341Z</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr"/>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z274" s="2" t="inlineStr"/>
+      <c r="AA274" s="2" t="inlineStr"/>
+      <c r="AB274" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:50.771046Z</t>
+        </is>
+      </c>
+      <c r="AD274" s="2" t="inlineStr"/>
+      <c r="AE274" s="2" t="inlineStr"/>
+      <c r="AF274" s="2" t="inlineStr"/>
+      <c r="AG274" s="2" t="inlineStr"/>
+      <c r="AH274" s="2" t="inlineStr"/>
+      <c r="AI274" s="2" t="inlineStr"/>
+      <c r="AJ274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>e860d608a5864f8a</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>0.695761</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr"/>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr"/>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>0.2755929327731092</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.569959Z</t>
+        </is>
+      </c>
+      <c r="S275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr"/>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z275" s="2" t="inlineStr"/>
+      <c r="AA275" s="2" t="inlineStr"/>
+      <c r="AB275" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:52.459313Z</t>
+        </is>
+      </c>
+      <c r="AD275" s="2" t="inlineStr"/>
+      <c r="AE275" s="2" t="inlineStr"/>
+      <c r="AF275" s="2" t="inlineStr"/>
+      <c r="AG275" s="2" t="inlineStr"/>
+      <c r="AH275" s="2" t="inlineStr"/>
+      <c r="AI275" s="2" t="inlineStr"/>
+      <c r="AJ275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>7038fc35b0fb4a89</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>0.563029</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr"/>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr"/>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>0.20331676978417268</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:38.040365Z</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr"/>
+      <c r="X276" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y276" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr"/>
+      <c r="AB276" s="2" t="inlineStr">
+        <is>
+          <t>1.7800</t>
+        </is>
+      </c>
+      <c r="AC276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:47.100660Z</t>
+        </is>
+      </c>
+      <c r="AD276" s="2" t="inlineStr"/>
+      <c r="AE276" s="2" t="inlineStr"/>
+      <c r="AF276" s="2" t="inlineStr"/>
+      <c r="AG276" s="2" t="inlineStr"/>
+      <c r="AH276" s="2" t="inlineStr"/>
+      <c r="AI276" s="2" t="inlineStr"/>
+      <c r="AJ276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>a6e542436f114084</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>0.615667</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr"/>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr"/>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>0.16521654954954945</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:38.979681Z</t>
+        </is>
+      </c>
+      <c r="S277" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
+      <c r="W277" s="2" t="inlineStr"/>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr"/>
+      <c r="AB277" s="2" t="inlineStr"/>
+      <c r="AC277" s="2" t="inlineStr"/>
+      <c r="AD277" s="2" t="inlineStr"/>
+      <c r="AE277" s="2" t="inlineStr"/>
+      <c r="AF277" s="2" t="inlineStr"/>
+      <c r="AG277" s="2" t="inlineStr"/>
+      <c r="AH277" s="2" t="inlineStr"/>
+      <c r="AI277" s="2" t="inlineStr"/>
+      <c r="AJ277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>4afd80f4a6844755</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>0.615411</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr"/>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>0.15458150691244243</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.149018Z</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr"/>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>0.460000</t>
+        </is>
+      </c>
+      <c r="AA278" s="2" t="inlineStr">
+        <is>
+          <t>-0.000829</t>
+        </is>
+      </c>
+      <c r="AB278" s="2" t="inlineStr">
+        <is>
+          <t>1.7550</t>
+        </is>
+      </c>
+      <c r="AC278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:48.636775Z</t>
+        </is>
+      </c>
+      <c r="AD278" s="2" t="inlineStr"/>
+      <c r="AE278" s="2" t="inlineStr"/>
+      <c r="AF278" s="2" t="inlineStr"/>
+      <c r="AG278" s="2" t="inlineStr"/>
+      <c r="AH278" s="2" t="inlineStr"/>
+      <c r="AI278" s="2" t="inlineStr"/>
+      <c r="AJ278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>b67e17b541554ce8</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>71675</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>0.631494</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr"/>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr"/>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>0.022119</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:14.324808Z</t>
+        </is>
+      </c>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr"/>
+      <c r="W279" s="2" t="inlineStr"/>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr"/>
+      <c r="AB279" s="2" t="inlineStr"/>
+      <c r="AC279" s="2" t="inlineStr"/>
+      <c r="AD279" s="2" t="inlineStr"/>
+      <c r="AE279" s="2" t="inlineStr"/>
+      <c r="AF279" s="2" t="inlineStr"/>
+      <c r="AG279" s="2" t="inlineStr"/>
+      <c r="AH279" s="2" t="inlineStr"/>
+      <c r="AI279" s="2" t="inlineStr"/>
+      <c r="AJ279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>c5d16584606a473f</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>0.75587</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr"/>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr"/>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>0.13609813688212935</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:16.114368Z</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
+      <c r="W280" s="2" t="inlineStr"/>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr"/>
+      <c r="AB280" s="2" t="inlineStr"/>
+      <c r="AC280" s="2" t="inlineStr"/>
+      <c r="AD280" s="2" t="inlineStr"/>
+      <c r="AE280" s="2" t="inlineStr"/>
+      <c r="AF280" s="2" t="inlineStr"/>
+      <c r="AG280" s="2" t="inlineStr"/>
+      <c r="AH280" s="2" t="inlineStr"/>
+      <c r="AI280" s="2" t="inlineStr"/>
+      <c r="AJ280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>69c05c0e21a84361</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>0.722571</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr"/>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr"/>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>0.37292065034965033</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:16.718069Z</t>
+        </is>
+      </c>
+      <c r="S281" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr"/>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr"/>
+      <c r="AB281" s="2" t="inlineStr"/>
+      <c r="AC281" s="2" t="inlineStr"/>
+      <c r="AD281" s="2" t="inlineStr"/>
+      <c r="AE281" s="2" t="inlineStr"/>
+      <c r="AF281" s="2" t="inlineStr"/>
+      <c r="AG281" s="2" t="inlineStr"/>
+      <c r="AH281" s="2" t="inlineStr"/>
+      <c r="AI281" s="2" t="inlineStr"/>
+      <c r="AJ281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>e3d1fd44e9ed4363</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>71675</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>0.653762</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr"/>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr"/>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>0.003412349650349644</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:59.654949Z</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr"/>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z282" s="2" t="inlineStr">
+        <is>
+          <t>0.650000</t>
+        </is>
+      </c>
+      <c r="AA282" s="2" t="inlineStr">
+        <is>
+          <t>-0.000350</t>
+        </is>
+      </c>
+      <c r="AB282" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC282" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:17.425685Z</t>
+        </is>
+      </c>
+      <c r="AD282" s="2" t="inlineStr"/>
+      <c r="AE282" s="2" t="inlineStr"/>
+      <c r="AF282" s="2" t="inlineStr"/>
+      <c r="AG282" s="2" t="inlineStr"/>
+      <c r="AH282" s="2" t="inlineStr"/>
+      <c r="AI282" s="2" t="inlineStr"/>
+      <c r="AJ282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>1f46225af3e84084</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>0.781713</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr"/>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr"/>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>0.172338</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:01.720459Z</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr"/>
+      <c r="X283" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr"/>
+      <c r="AB283" s="2" t="inlineStr"/>
+      <c r="AC283" s="2" t="inlineStr"/>
+      <c r="AD283" s="2" t="inlineStr"/>
+      <c r="AE283" s="2" t="inlineStr"/>
+      <c r="AF283" s="2" t="inlineStr"/>
+      <c r="AG283" s="2" t="inlineStr"/>
+      <c r="AH283" s="2" t="inlineStr"/>
+      <c r="AI283" s="2" t="inlineStr"/>
+      <c r="AJ283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>e1503593890c47b3</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>0.743939</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr"/>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr"/>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>0.3942886503496504</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:02.419049Z</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="inlineStr"/>
+      <c r="W284" s="2" t="inlineStr"/>
+      <c r="X284" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr"/>
+      <c r="AB284" s="2" t="inlineStr"/>
+      <c r="AC284" s="2" t="inlineStr"/>
+      <c r="AD284" s="2" t="inlineStr"/>
+      <c r="AE284" s="2" t="inlineStr"/>
+      <c r="AF284" s="2" t="inlineStr"/>
+      <c r="AG284" s="2" t="inlineStr"/>
+      <c r="AH284" s="2" t="inlineStr"/>
+      <c r="AI284" s="2" t="inlineStr"/>
+      <c r="AJ284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>d186e5c257b24465</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>0.577819</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr"/>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr"/>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>-0.062468769784172706</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:04.421117Z</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr"/>
+      <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr"/>
+      <c r="X285" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr"/>
+      <c r="AA285" s="2" t="inlineStr"/>
+      <c r="AB285" s="2" t="inlineStr"/>
+      <c r="AC285" s="2" t="inlineStr"/>
+      <c r="AD285" s="2" t="inlineStr"/>
+      <c r="AE285" s="2" t="inlineStr"/>
+      <c r="AF285" s="2" t="inlineStr"/>
+      <c r="AG285" s="2" t="inlineStr"/>
+      <c r="AH285" s="2" t="inlineStr"/>
+      <c r="AI285" s="2" t="inlineStr"/>
+      <c r="AJ285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>92801d4063db4cce</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>0.542991</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr"/>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr"/>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>-0.1567086996996997</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:05.994937Z</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr"/>
+      <c r="X286" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr"/>
+      <c r="AA286" s="2" t="inlineStr"/>
+      <c r="AB286" s="2" t="inlineStr"/>
+      <c r="AC286" s="2" t="inlineStr"/>
+      <c r="AD286" s="2" t="inlineStr"/>
+      <c r="AE286" s="2" t="inlineStr"/>
+      <c r="AF286" s="2" t="inlineStr"/>
+      <c r="AG286" s="2" t="inlineStr"/>
+      <c r="AH286" s="2" t="inlineStr"/>
+      <c r="AI286" s="2" t="inlineStr"/>
+      <c r="AJ286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>6bac855115f34a02</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>0.700157</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr"/>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr"/>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>0.3199288631178707</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:10.514790Z</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr"/>
+      <c r="X287" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr"/>
+      <c r="AA287" s="2" t="inlineStr"/>
+      <c r="AB287" s="2" t="inlineStr"/>
+      <c r="AC287" s="2" t="inlineStr"/>
+      <c r="AD287" s="2" t="inlineStr"/>
+      <c r="AE287" s="2" t="inlineStr"/>
+      <c r="AF287" s="2" t="inlineStr"/>
+      <c r="AG287" s="2" t="inlineStr"/>
+      <c r="AH287" s="2" t="inlineStr"/>
+      <c r="AI287" s="2" t="inlineStr"/>
+      <c r="AJ287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>0422ded690714d73</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>b73645bf1ecd543fdd6eef3fb18bf1f86790dae2d994242a68d3628f34298e3b</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>0.700561</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr"/>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr"/>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>0.1005609999999999</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:11.884096Z</t>
+        </is>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr"/>
+      <c r="X288" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y288" s="2" t="inlineStr"/>
+      <c r="Z288" s="2" t="inlineStr"/>
+      <c r="AA288" s="2" t="inlineStr"/>
+      <c r="AB288" s="2" t="inlineStr"/>
+      <c r="AC288" s="2" t="inlineStr"/>
+      <c r="AD288" s="2" t="inlineStr"/>
+      <c r="AE288" s="2" t="inlineStr"/>
+      <c r="AF288" s="2" t="inlineStr"/>
+      <c r="AG288" s="2" t="inlineStr"/>
+      <c r="AH288" s="2" t="inlineStr"/>
+      <c r="AI288" s="2" t="inlineStr"/>
+      <c r="AJ288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>c0c2c25ef7a24e45</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>0.781485</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="2" t="inlineStr"/>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr"/>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>0.17210999999999999</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:21.351080Z</t>
+        </is>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr"/>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>0.610000</t>
+        </is>
+      </c>
+      <c r="AA289" s="2" t="inlineStr">
+        <is>
+          <t>0.000625</t>
+        </is>
+      </c>
+      <c r="AB289" s="2" t="inlineStr">
+        <is>
+          <t>1.2821</t>
+        </is>
+      </c>
+      <c r="AC289" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:02.152537Z</t>
+        </is>
+      </c>
+      <c r="AD289" s="2" t="inlineStr"/>
+      <c r="AE289" s="2" t="inlineStr"/>
+      <c r="AF289" s="2" t="inlineStr"/>
+      <c r="AG289" s="2" t="inlineStr"/>
+      <c r="AH289" s="2" t="inlineStr"/>
+      <c r="AI289" s="2" t="inlineStr"/>
+      <c r="AJ289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>fe2fe15aa0004a81</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>0.74376</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr"/>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr"/>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>0.39410965034965034</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:22.081076Z</t>
+        </is>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr"/>
+      <c r="U290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="inlineStr"/>
+      <c r="W290" s="2" t="inlineStr"/>
+      <c r="X290" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr"/>
+      <c r="AA290" s="2" t="inlineStr"/>
+      <c r="AB290" s="2" t="inlineStr"/>
+      <c r="AC290" s="2" t="inlineStr"/>
+      <c r="AD290" s="2" t="inlineStr"/>
+      <c r="AE290" s="2" t="inlineStr"/>
+      <c r="AF290" s="2" t="inlineStr"/>
+      <c r="AG290" s="2" t="inlineStr"/>
+      <c r="AH290" s="2" t="inlineStr"/>
+      <c r="AI290" s="2" t="inlineStr"/>
+      <c r="AJ290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>d9e889dd70f547bb</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>0.577702</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="2" t="inlineStr"/>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr"/>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>-0.06258576978417263</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.252919Z</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="inlineStr"/>
+      <c r="W291" s="2" t="inlineStr"/>
+      <c r="X291" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr"/>
+      <c r="AA291" s="2" t="inlineStr"/>
+      <c r="AB291" s="2" t="inlineStr"/>
+      <c r="AC291" s="2" t="inlineStr"/>
+      <c r="AD291" s="2" t="inlineStr"/>
+      <c r="AE291" s="2" t="inlineStr"/>
+      <c r="AF291" s="2" t="inlineStr"/>
+      <c r="AG291" s="2" t="inlineStr"/>
+      <c r="AH291" s="2" t="inlineStr"/>
+      <c r="AI291" s="2" t="inlineStr"/>
+      <c r="AJ291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>7199ec87dda14ee2</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>0.542909</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr"/>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr"/>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>-0.15679069969969972</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.762948Z</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr"/>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr"/>
+      <c r="AB292" s="2" t="inlineStr"/>
+      <c r="AC292" s="2" t="inlineStr"/>
+      <c r="AD292" s="2" t="inlineStr"/>
+      <c r="AE292" s="2" t="inlineStr"/>
+      <c r="AF292" s="2" t="inlineStr"/>
+      <c r="AG292" s="2" t="inlineStr"/>
+      <c r="AH292" s="2" t="inlineStr"/>
+      <c r="AI292" s="2" t="inlineStr"/>
+      <c r="AJ292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2484cecb06cb4848</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>0.69991</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr"/>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr"/>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>0.3295396296296297</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:27.602644Z</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr"/>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr"/>
+      <c r="AB293" s="2" t="inlineStr"/>
+      <c r="AC293" s="2" t="inlineStr"/>
+      <c r="AD293" s="2" t="inlineStr"/>
+      <c r="AE293" s="2" t="inlineStr"/>
+      <c r="AF293" s="2" t="inlineStr"/>
+      <c r="AG293" s="2" t="inlineStr"/>
+      <c r="AH293" s="2" t="inlineStr"/>
+      <c r="AI293" s="2" t="inlineStr"/>
+      <c r="AJ293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>d6cd10135c454548</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>0.700453</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr"/>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr"/>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>0.1004529999999999</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:28.911173Z</t>
+        </is>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr"/>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr"/>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr"/>
+      <c r="AB294" s="2" t="inlineStr"/>
+      <c r="AC294" s="2" t="inlineStr"/>
+      <c r="AD294" s="2" t="inlineStr"/>
+      <c r="AE294" s="2" t="inlineStr"/>
+      <c r="AF294" s="2" t="inlineStr"/>
+      <c r="AG294" s="2" t="inlineStr"/>
+      <c r="AH294" s="2" t="inlineStr"/>
+      <c r="AI294" s="2" t="inlineStr"/>
+      <c r="AJ294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>f4e06e8d402e48eb</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>0.743312</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr"/>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr"/>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>0.36308386311787066</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:10.020929Z</t>
+        </is>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr"/>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr"/>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr"/>
+      <c r="AA295" s="2" t="inlineStr"/>
+      <c r="AB295" s="2" t="inlineStr"/>
+      <c r="AC295" s="2" t="inlineStr"/>
+      <c r="AD295" s="2" t="inlineStr"/>
+      <c r="AE295" s="2" t="inlineStr"/>
+      <c r="AF295" s="2" t="inlineStr"/>
+      <c r="AG295" s="2" t="inlineStr"/>
+      <c r="AH295" s="2" t="inlineStr"/>
+      <c r="AI295" s="2" t="inlineStr"/>
+      <c r="AJ295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>7741e502304446d1</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>0.577151</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr"/>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr"/>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>-0.06313676978417271</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.643542Z</t>
+        </is>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr"/>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr"/>
+      <c r="AA296" s="2" t="inlineStr"/>
+      <c r="AB296" s="2" t="inlineStr"/>
+      <c r="AC296" s="2" t="inlineStr"/>
+      <c r="AD296" s="2" t="inlineStr"/>
+      <c r="AE296" s="2" t="inlineStr"/>
+      <c r="AF296" s="2" t="inlineStr"/>
+      <c r="AG296" s="2" t="inlineStr"/>
+      <c r="AH296" s="2" t="inlineStr"/>
+      <c r="AI296" s="2" t="inlineStr"/>
+      <c r="AJ296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>48635e686c8b4edc</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>0.542508</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr"/>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr"/>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>-0.1571916996996997</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:13.149551Z</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr"/>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr"/>
+      <c r="AB297" s="2" t="inlineStr"/>
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="2" t="inlineStr"/>
+      <c r="AE297" s="2" t="inlineStr"/>
+      <c r="AF297" s="2" t="inlineStr"/>
+      <c r="AG297" s="2" t="inlineStr"/>
+      <c r="AH297" s="2" t="inlineStr"/>
+      <c r="AI297" s="2" t="inlineStr"/>
+      <c r="AJ297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>bcd5d03f9677471d</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>0.699367</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr"/>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr"/>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>0.31913886311787065</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:16.500524Z</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr"/>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr"/>
+      <c r="AB298" s="2" t="inlineStr"/>
+      <c r="AC298" s="2" t="inlineStr"/>
+      <c r="AD298" s="2" t="inlineStr"/>
+      <c r="AE298" s="2" t="inlineStr"/>
+      <c r="AF298" s="2" t="inlineStr"/>
+      <c r="AG298" s="2" t="inlineStr"/>
+      <c r="AH298" s="2" t="inlineStr"/>
+      <c r="AI298" s="2" t="inlineStr"/>
+      <c r="AJ298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>8bca806089da4abd</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>1af3798e94d5b1473865bcb78b085884572681551a9b34a966767bcfe3a6e48f</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>0.70043</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr"/>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr"/>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>0.10042999999999991</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:17.753313Z</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr"/>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr"/>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr"/>
+      <c r="AB299" s="2" t="inlineStr"/>
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="2" t="inlineStr"/>
+      <c r="AE299" s="2" t="inlineStr"/>
+      <c r="AF299" s="2" t="inlineStr"/>
+      <c r="AG299" s="2" t="inlineStr"/>
+      <c r="AH299" s="2" t="inlineStr"/>
+      <c r="AI299" s="2" t="inlineStr"/>
+      <c r="AJ299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>4ecf7d1d89ff4afc</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>0.743264</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr"/>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr"/>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>0.3835517697841727</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.113763Z</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr"/>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr"/>
+      <c r="AB300" s="2" t="inlineStr"/>
+      <c r="AC300" s="2" t="inlineStr"/>
+      <c r="AD300" s="2" t="inlineStr"/>
+      <c r="AE300" s="2" t="inlineStr"/>
+      <c r="AF300" s="2" t="inlineStr"/>
+      <c r="AG300" s="2" t="inlineStr"/>
+      <c r="AH300" s="2" t="inlineStr"/>
+      <c r="AI300" s="2" t="inlineStr"/>
+      <c r="AJ300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>19e786c0c8d04a75</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>0.577178</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr"/>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr"/>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>-0.06310976978417271</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.286884Z</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr"/>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr"/>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr"/>
+      <c r="AB301" s="2" t="inlineStr"/>
+      <c r="AC301" s="2" t="inlineStr"/>
+      <c r="AD301" s="2" t="inlineStr"/>
+      <c r="AE301" s="2" t="inlineStr"/>
+      <c r="AF301" s="2" t="inlineStr"/>
+      <c r="AG301" s="2" t="inlineStr"/>
+      <c r="AH301" s="2" t="inlineStr"/>
+      <c r="AI301" s="2" t="inlineStr"/>
+      <c r="AJ301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>de98adef3dba4b8b</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>0.542519</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr"/>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>-0.15718069969969972</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.818736Z</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr"/>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr"/>
+      <c r="AB302" s="2" t="inlineStr"/>
+      <c r="AC302" s="2" t="inlineStr"/>
+      <c r="AD302" s="2" t="inlineStr"/>
+      <c r="AE302" s="2" t="inlineStr"/>
+      <c r="AF302" s="2" t="inlineStr"/>
+      <c r="AG302" s="2" t="inlineStr"/>
+      <c r="AH302" s="2" t="inlineStr"/>
+      <c r="AI302" s="2" t="inlineStr"/>
+      <c r="AJ302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>eddc3a87699c4bb0</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>0.699272</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr"/>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr"/>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>0.3190438631178707</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:59.578708Z</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr"/>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr"/>
+      <c r="AB303" s="2" t="inlineStr"/>
+      <c r="AC303" s="2" t="inlineStr"/>
+      <c r="AD303" s="2" t="inlineStr"/>
+      <c r="AE303" s="2" t="inlineStr"/>
+      <c r="AF303" s="2" t="inlineStr"/>
+      <c r="AG303" s="2" t="inlineStr"/>
+      <c r="AH303" s="2" t="inlineStr"/>
+      <c r="AI303" s="2" t="inlineStr"/>
+      <c r="AJ303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>dcaffaf42f834c93</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>0.700273</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr"/>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr"/>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>0.10027299999999995</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.754763Z</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr"/>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr"/>
+      <c r="AB304" s="2" t="inlineStr"/>
+      <c r="AC304" s="2" t="inlineStr"/>
+      <c r="AD304" s="2" t="inlineStr"/>
+      <c r="AE304" s="2" t="inlineStr"/>
+      <c r="AF304" s="2" t="inlineStr"/>
+      <c r="AG304" s="2" t="inlineStr"/>
+      <c r="AH304" s="2" t="inlineStr"/>
+      <c r="AI304" s="2" t="inlineStr"/>
+      <c r="AJ304" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ255"/>
+  <autoFilter ref="A1:AJ304"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/valorant-tiered-elo.xlsx
+++ b/data/research/model_ledgers/valorant-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$309</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ304"/>
+  <dimension ref="A1:AJ309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31974,8 +31974,518 @@
       <c r="AI304" s="2" t="inlineStr"/>
       <c r="AJ304" s="2" t="inlineStr"/>
     </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>ab574d270dc94ba9</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>72723</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>0.577074</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr"/>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr"/>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>-0.0632137697841727</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:09.718182Z</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr"/>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr"/>
+      <c r="AB305" s="2" t="inlineStr"/>
+      <c r="AC305" s="2" t="inlineStr"/>
+      <c r="AD305" s="2" t="inlineStr"/>
+      <c r="AE305" s="2" t="inlineStr"/>
+      <c r="AF305" s="2" t="inlineStr"/>
+      <c r="AG305" s="2" t="inlineStr"/>
+      <c r="AH305" s="2" t="inlineStr"/>
+      <c r="AI305" s="2" t="inlineStr"/>
+      <c r="AJ305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>f7d6ce11092a4ce4</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>0.542435</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr"/>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr"/>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>-0.1572646996996997</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:10.347731Z</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr"/>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr"/>
+      <c r="AB306" s="2" t="inlineStr"/>
+      <c r="AC306" s="2" t="inlineStr"/>
+      <c r="AD306" s="2" t="inlineStr"/>
+      <c r="AE306" s="2" t="inlineStr"/>
+      <c r="AF306" s="2" t="inlineStr"/>
+      <c r="AG306" s="2" t="inlineStr"/>
+      <c r="AH306" s="2" t="inlineStr"/>
+      <c r="AI306" s="2" t="inlineStr"/>
+      <c r="AJ306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>26d3b514f24d4af7</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>74125</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>0.637346</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr"/>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr"/>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>0.10682956807511734</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:13.105417Z</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr"/>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr"/>
+      <c r="AB307" s="2" t="inlineStr"/>
+      <c r="AC307" s="2" t="inlineStr"/>
+      <c r="AD307" s="2" t="inlineStr"/>
+      <c r="AE307" s="2" t="inlineStr"/>
+      <c r="AF307" s="2" t="inlineStr"/>
+      <c r="AG307" s="2" t="inlineStr"/>
+      <c r="AH307" s="2" t="inlineStr"/>
+      <c r="AI307" s="2" t="inlineStr"/>
+      <c r="AJ307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>197d175c2d2945bc</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>0.698711</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr"/>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr"/>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>0.31848286311787066</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:13.626555Z</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr"/>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr"/>
+      <c r="AB308" s="2" t="inlineStr"/>
+      <c r="AC308" s="2" t="inlineStr"/>
+      <c r="AD308" s="2" t="inlineStr"/>
+      <c r="AE308" s="2" t="inlineStr"/>
+      <c r="AF308" s="2" t="inlineStr"/>
+      <c r="AG308" s="2" t="inlineStr"/>
+      <c r="AH308" s="2" t="inlineStr"/>
+      <c r="AI308" s="2" t="inlineStr"/>
+      <c r="AJ308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>76a0aa2b8a5b44c9</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>73525</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>0.700072</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr"/>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr"/>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>0.10007199999999994</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:15.156257Z</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr"/>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr"/>
+      <c r="AB309" s="2" t="inlineStr"/>
+      <c r="AC309" s="2" t="inlineStr"/>
+      <c r="AD309" s="2" t="inlineStr"/>
+      <c r="AE309" s="2" t="inlineStr"/>
+      <c r="AF309" s="2" t="inlineStr"/>
+      <c r="AG309" s="2" t="inlineStr"/>
+      <c r="AH309" s="2" t="inlineStr"/>
+      <c r="AI309" s="2" t="inlineStr"/>
+      <c r="AJ309" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ304"/>
+  <autoFilter ref="A1:AJ309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>